--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28FED34-4DCA-4E9A-A307-6F1A8FC04492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDDB82-2EEF-41EF-8404-CCA8DB5E24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="60" windowWidth="20355" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -44,55 +44,52 @@
     <t>LastAuditYear__c</t>
   </si>
   <si>
-    <t>fieldFirstName</t>
-  </si>
-  <si>
     <t>none</t>
   </si>
   <si>
     <t>Automation Runtime</t>
   </si>
   <si>
-    <t>fieldLastName</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
-    <t>fieldPhone</t>
-  </si>
-  <si>
-    <t>fieldUserRole__c</t>
-  </si>
-  <si>
     <t>Secondary</t>
   </si>
   <si>
-    <t>fieldMailingStreet</t>
-  </si>
-  <si>
     <t>Street 1</t>
   </si>
   <si>
-    <t>fieldMailingCity</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
     <t>GA</t>
   </si>
   <si>
-    <t>fieldMailingPostalCode</t>
-  </si>
-  <si>
-    <t>fieldMailingCountry</t>
-  </si>
-  <si>
     <t>US</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>UserRole__c</t>
+  </si>
+  <si>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>AK</t>
   </si>
 </sst>
 </file>
@@ -424,13 +421,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -452,7 +449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -471,13 +468,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,103 +485,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>9578345724</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDDB82-2EEF-41EF-8404-CCA8DB5E24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C9AB14-BF35-409D-80E0-62566758C761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -59,12 +59,6 @@
     <t>Street 1</t>
   </si>
   <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
     <t>FirstName</t>
   </si>
   <si>
@@ -90,13 +84,28 @@
   </si>
   <si>
     <t>AK</t>
+  </si>
+  <si>
+    <t>Role__c</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>(879) 573-4890</t>
+  </si>
+  <si>
+    <t>AK: Alaska</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +116,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -131,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -140,6 +155,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
@@ -489,11 +508,11 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -501,10 +520,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -512,21 +531,21 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>9578345724</v>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -534,10 +553,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -545,10 +564,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -556,10 +575,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -567,21 +586,32 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>12345</v>
+        <v>17</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
+      <c r="B10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDDB82-2EEF-41EF-8404-CCA8DB5E24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5975520C-C4CF-40A8-B8F7-9410E975BDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="15375" windowHeight="7785" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -59,37 +59,37 @@
     <t>Street 1</t>
   </si>
   <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>UserRole__c</t>
+  </si>
+  <si>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>AK: Alaska</t>
+  </si>
+  <si>
     <t>GA</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>UserRole__c</t>
-  </si>
-  <si>
-    <t>MailingStreet</t>
-  </si>
-  <si>
-    <t>MailingCity</t>
-  </si>
-  <si>
-    <t>State__c</t>
-  </si>
-  <si>
-    <t>MailingPostalCode</t>
-  </si>
-  <si>
-    <t>MailingCountry</t>
-  </si>
-  <si>
-    <t>AK</t>
   </si>
 </sst>
 </file>
@@ -421,13 +421,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -449,7 +449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -468,13 +468,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,29 +485,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -518,70 +518,70 @@
         <v>9578345724</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="C9">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C9AB14-BF35-409D-80E0-62566758C761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35F6337-17C4-48C3-9AA9-DD739A2F709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -84,12 +84,6 @@
   </si>
   <si>
     <t>AK</t>
-  </si>
-  <si>
-    <t>Role__c</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>(879) 573-4890</t>
@@ -440,13 +434,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -468,7 +462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -486,14 +480,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,117 +498,107 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCDDB82-2EEF-41EF-8404-CCA8DB5E24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E879DF-7956-4900-AB03-41FCC9060F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>Street 1</t>
   </si>
   <si>
-    <t>GA</t>
-  </si>
-  <si>
     <t>US</t>
   </si>
   <si>
@@ -90,6 +87,9 @@
   </si>
   <si>
     <t>AK</t>
+  </si>
+  <si>
+    <t>KS: Kansas</t>
   </si>
 </sst>
 </file>
@@ -421,13 +421,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -449,7 +449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -468,13 +468,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,29 +485,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -518,70 +518,70 @@
         <v>9578345724</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="C9">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
